--- a/src/physion/acquisition/DataTable.xlsx
+++ b/src/physion/acquisition/DataTable.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Recordings" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Subjects" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Analysis" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="--whatever--" sheetId="4" state="visible" r:id="rId6"/>
@@ -34,82 +34,82 @@
     <t xml:space="preserve">time</t>
   </si>
   <si>
+    <t xml:space="preserve">FOV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">force_to_visualStimTimestamps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reverse_photodiodeSignal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Locomotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VisualStim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FaceMotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pupil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_FaceCamera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processed_CaImaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_CaImaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_episode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lignée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acronyme lignée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sexe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. naissance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chirurgie 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. chirurgie 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chirurgie 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. chirurgie 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dilution virus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Génotype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espèce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Souche</t>
+  </si>
+  <si>
     <t xml:space="preserve">recording</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">force_to_visualStimTimestamps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reverse_photodiodeSignal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Locomotion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VisualStim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FaceMotion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pupil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_FaceCamera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processed_CaImaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_CaImaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_episode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lignée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acronyme lignée</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sexe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. naissance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chirurgie 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. chirurgie 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chirurgie 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. chirurgie 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dilution virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Génotype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espèce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Souche</t>
   </si>
 </sst>
 </file>
@@ -509,11 +509,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.84"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="true" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -521,47 +522,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="P1" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E5" s="7"/>
@@ -593,46 +595,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="N1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>27</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +661,7 @@
   <sheetData>
     <row r="1" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/src/physion/acquisition/DataTable.xlsx
+++ b/src/physion/acquisition/DataTable.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t xml:space="preserve">subject</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t xml:space="preserve">recording</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protocol</t>
   </si>
 </sst>
 </file>
@@ -120,7 +123,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -188,6 +191,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -269,7 +279,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -294,6 +304,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -302,10 +316,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
@@ -315,6 +325,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -513,60 +531,58 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.84"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="2" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="7" customFormat="true" ht="19.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="6"/>
       <c r="P1" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E5" s="7"/>
+      <c r="D5" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -587,7 +603,7 @@
   <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="15.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="15.92"/>
   </cols>
   <sheetData>
     <row r="1" s="11" customFormat="true" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -653,19 +669,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.08"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
         <v>28</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13"/>
+      <c r="A2" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
